--- a/docs/0OMsoqOg9GiJ2xusVHM2/.gitbook/assets/IO - Template servizi - Diritti di segreteria.xlsx
+++ b/docs/0OMsoqOg9GiJ2xusVHM2/.gitbook/assets/IO - Template servizi - Diritti di segreteria.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="82">
   <si>
     <r>
       <t xml:space="preserve">
@@ -145,7 +145,7 @@
     <t>Utilizza il testo indicato per il pulsante. Inserisci il link alla pagina web che rimanda al servizio.</t>
   </si>
   <si>
-    <t>Visualizza tabella diritti di segreteria</t>
+    <t>n/a</t>
   </si>
   <si>
     <t>Link a termini e condizioni d'uso</t>
@@ -439,8 +439,8 @@
         <rFont val="Titillium Web"/>
       </rPr>
       <t xml:space="preserve">
-Puoi pagare direttamente in app premendo “Vedi Avviso”, oppure tramite tutti i canali di pagamento della piattaforma pagoPA e le altre modalità di pagamento offerte dell'ente creditore.
-Se hai già provveduto a pagare l'avviso ignora questo messaggio.
+Puoi pagare direttamente in app premendo “Paga”, oppure tramite tutti i canali di pagamento della piattaforma pagoPA e le altre modalità di pagamento offerte dell'ente creditore.
+Se hai già provveduto a pagare l'avviso, ignora questo messaggio.
 Per maggiori informazioni o per richiedere assistenza, contattaci tramite i canali che trovi nella scheda servizio.
 In fase di pagamento, se previsto dall'ente, l'importo riportato nel messaggio potrebbe subire variazioni.</t>
     </r>
@@ -532,7 +532,7 @@
     </r>
   </si>
   <si>
-    <t>Vedi Avviso</t>
+    <t>Paga (inserito automaticamente dall'app se il messaggio prevede un avviso di pagamento pagoPA)</t>
   </si>
   <si>
     <r>
@@ -552,7 +552,7 @@
       <rPr>
         <b/>
       </rPr>
-      <t>Allegato (Premium)</t>
+      <t>Allegato</t>
     </r>
     <r>
       <rPr/>
@@ -611,14 +611,6 @@
       </rPr>
       <t>Note aggiuntive</t>
     </r>
-  </si>
-  <si>
-    <t>✨ Messaggio Premium — Se hai un contratto Premium, ti consigliamo di configurare questo messaggio con promemoria Premium: i destinatari verranno avvisati dell‘avvicinarsi della scadenza tramite notifica push.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Promemoria automatici — Messaggi Premium
-Impostando il messaggio di Avviso di pagamento come Messaggio Premium, disponibile a seconda della tipologia di contratto sottoscritto dall’ente, non è necessario inviare il seguente messaggio di promemoria.
-Gli utenti che hanno dato il loro consenso, infatti, riceveranno automaticamente una notifica push sui loro dispositivi all’avvicinarsi della scadenza.</t>
   </si>
   <si>
     <t xml:space="preserve">Mancato pagamento
@@ -1336,13 +1328,13 @@
         <v>80</v>
       </c>
       <c r="B11" s="34" t="s">
-        <v>81</v>
+        <v>53</v>
       </c>
       <c r="C11" s="34" t="s">
-        <v>82</v>
+        <v>53</v>
       </c>
       <c r="D11" s="34" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
   </sheetData>
